--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0042178D-334F-4F92-BDE3-250838EAE24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF94DA4-8B2F-405D-BF7F-552AF5E510EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
@@ -465,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A26D15-6A7E-4936-9C3A-EF35D57FBB9C}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" style="3" bestFit="1" customWidth="1"/>
@@ -505,23 +505,20 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>60</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>35</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -531,22 +528,21 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>80</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>8</v>
       </c>
-      <c r="F3"/>
       <c r="G3">
         <v>25000</v>
       </c>
@@ -555,23 +551,20 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>35</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -579,6 +572,36 @@
       <c r="H4">
         <v>0</v>
       </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF94DA4-8B2F-405D-BF7F-552AF5E510EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B29B912-D0FB-480D-9ACF-581799B49CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Machine_Rate_EUR_hr</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>Tool_Life_Pcs</t>
+  </si>
+  <si>
+    <t>CNC Machining</t>
+  </si>
+  <si>
+    <t>HP Multi Jet Fusion</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.90625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -505,6 +511,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -528,6 +537,9 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -551,6 +563,9 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B29B912-D0FB-480D-9ACF-581799B49CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241C99D3-C420-4E3E-A08B-7B5050906402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
+    <workbookView xWindow="-43305" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Machine_Rate_EUR_hr</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Tooling_Cost_EUR</t>
   </si>
   <si>
-    <t>CNC</t>
-  </si>
-  <si>
     <t>1.3</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
   </si>
   <si>
     <t>1.2</t>
-  </si>
-  <si>
-    <t>HP MJF</t>
   </si>
   <si>
     <t>1.1</t>
@@ -128,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -136,6 +130,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,10 +471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A26D15-6A7E-4936-9C3A-EF35D57FBB9C}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.90625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -485,11 +485,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>11</v>
+      <c r="A1" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -507,29 +507,29 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>60</v>
-      </c>
-      <c r="D2">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>0</v>
       </c>
       <c r="H2" s="3">
@@ -537,86 +537,56 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>80</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" s="3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>25000</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3">
         <v>35</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
         <v>2</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241C99D3-C420-4E3E-A08B-7B5050906402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCEA0AE-D662-4B32-ACB5-AFCD26C7640B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43305" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Machine_Rate_EUR_hr</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>HP Multi Jet Fusion</t>
+  </si>
+  <si>
+    <t>Project_Life_Years</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A26D15-6A7E-4936-9C3A-EF35D57FBB9C}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="5" bestFit="1" customWidth="1"/>
@@ -482,9 +485,10 @@
     <col min="6" max="6" width="11.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -509,8 +513,11 @@
       <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -535,8 +542,11 @@
       <c r="H2" s="3">
         <v>0</v>
       </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -561,8 +571,11 @@
       <c r="H3" s="3">
         <v>500000</v>
       </c>
+      <c r="I3" s="3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -585,6 +598,9 @@
         <v>0</v>
       </c>
       <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
         <v>0</v>
       </c>
     </row>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCEA0AE-D662-4B32-ACB5-AFCD26C7640B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F095157-5918-458A-839A-667A96036A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>Machine_Rate_EUR_hr</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Project_Life_Years</t>
+  </si>
+  <si>
+    <t>Cycle_Time_sec</t>
+  </si>
+  <si>
+    <t>Scrap_Rate</t>
   </si>
 </sst>
 </file>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -140,6 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A26D15-6A7E-4936-9C3A-EF35D57FBB9C}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="5" bestFit="1" customWidth="1"/>
@@ -486,9 +493,11 @@
     <col min="7" max="7" width="16.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -516,8 +525,14 @@
       <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -545,8 +560,14 @@
       <c r="I2" s="3">
         <v>0</v>
       </c>
+      <c r="J2" s="3">
+        <v>360</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -574,8 +595,14 @@
       <c r="I3" s="3">
         <v>10</v>
       </c>
+      <c r="J3" s="3">
+        <v>30</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.05</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -602,6 +629,12 @@
       </c>
       <c r="I4" s="3">
         <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>420</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F095157-5918-458A-839A-667A96036A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D50C36-4EE8-492B-B730-6D7AD4A3E0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="K4" s="6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D50C36-4EE8-492B-B730-6D7AD4A3E0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1117FA1-E4D1-4419-B9BD-254A74DD0392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Machine_Rate_EUR_hr</t>
   </si>
@@ -90,6 +90,42 @@
   </si>
   <si>
     <t>Scrap_Rate</t>
+  </si>
+  <si>
+    <t>Yield_Rate</t>
+  </si>
+  <si>
+    <t>OEE</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Batch_size</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.03</t>
   </si>
 </sst>
 </file>
@@ -131,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -146,7 +182,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A26D15-6A7E-4936-9C3A-EF35D57FBB9C}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="5" bestFit="1" customWidth="1"/>
@@ -494,10 +529,13 @@
     <col min="8" max="8" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -528,11 +566,20 @@
       <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -563,11 +610,20 @@
       <c r="J2" s="3">
         <v>360</v>
       </c>
-      <c r="K2" s="6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="3">
+        <v>50</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -598,11 +654,20 @@
       <c r="J3" s="3">
         <v>30</v>
       </c>
-      <c r="K3" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -633,9 +698,74 @@
       <c r="J4" s="3">
         <v>600</v>
       </c>
-      <c r="K4" s="6">
-        <v>0.03</v>
-      </c>
+      <c r="K4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="3">
+        <v>100</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="J12"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/masterdata/Technology_Cost_Library.xlsx
+++ b/data/masterdata/Technology_Cost_Library.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1117FA1-E4D1-4419-B9BD-254A74DD0392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
+    <workbookView xWindow="-44805" yWindow="0" windowWidth="16110" windowHeight="6060" xr2:uid="{70077FAF-5FCD-4C27-AB66-FA9E6CA2A8C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
